--- a/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
+++ b/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\crane_lifting_capacity\data\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4735630-68D1-4100-900F-17124241928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256E11F3-8E54-4093-9648-A9C3B4F3B69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15315" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="23" r:id="rId1"/>
@@ -66,9 +66,6 @@
     <t>Оплата труда машинистов, руб.</t>
   </si>
   <si>
-    <t>mobile</t>
-  </si>
-  <si>
     <t>Сборник</t>
   </si>
   <si>
@@ -89,6 +86,9 @@
   <si>
     <t>Максимальная грузоподъемность</t>
   </si>
+  <si>
+    <t>Спецшасси автомобильного типа</t>
+  </si>
 </sst>
 </file>
 
@@ -97,7 +97,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +139,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -563,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -686,6 +694,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1006,7 +1017,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="1" customWidth="1"/>
     <col min="3" max="5" width="11.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" style="1" customWidth="1"/>
     <col min="7" max="9" width="11.85546875" style="1" customWidth="1"/>
@@ -1042,8 +1053,8 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
+      <c r="B3" s="42" t="s">
+        <v>17</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>9</v>
@@ -1051,10 +1062,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="37">
         <v>1147.3800000000001</v>
@@ -1062,13 +1073,13 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" s="37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="38">
         <v>300</v>
@@ -1076,7 +1087,7 @@
     </row>
     <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -1098,7 +1109,7 @@
     <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="29"/>
       <c r="C7" s="39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>

--- a/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
+++ b/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\crane_lifting_capacity\data\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256E11F3-8E54-4093-9648-A9C3B4F3B69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3ECFFB-2127-4AF4-A3B0-1A84D1B3AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
+    <workbookView xWindow="38280" yWindow="-6060" windowWidth="29040" windowHeight="15840" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="23" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="20">
   <si>
     <t>Вылет, м</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>Спецшасси автомобильного типа</t>
+  </si>
+  <si>
+    <t>39.0</t>
+  </si>
+  <si>
+    <t>78.0</t>
   </si>
 </sst>
 </file>
@@ -660,21 +666,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -687,6 +684,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -694,9 +703,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1034,7 +1040,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1045,7 +1051,7 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="34">
         <v>14644.63</v>
       </c>
     </row>
@@ -1053,10 +1059,10 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="34" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1067,7 +1073,7 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="34">
         <v>1147.3800000000001</v>
       </c>
     </row>
@@ -1078,116 +1084,116 @@
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="35">
         <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="42"/>
     </row>
     <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="29"/>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="42"/>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="38">
         <v>14.7</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="38">
         <v>19.600000000000001</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="38">
         <v>24.4</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="38">
         <v>29.3</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="38">
         <v>34.200000000000003</v>
       </c>
-      <c r="I8" s="31">
-        <v>39</v>
-      </c>
-      <c r="J8" s="31">
+      <c r="I8" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="38">
         <v>43.9</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="38">
         <v>48.7</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="38">
         <v>53.6</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="38">
         <v>58.5</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="38">
         <v>63.3</v>
       </c>
-      <c r="O8" s="31">
+      <c r="O8" s="38">
         <v>68.2</v>
       </c>
-      <c r="P8" s="31">
+      <c r="P8" s="38">
         <v>73.099999999999994</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="38">
         <v>77.2</v>
       </c>
-      <c r="R8" s="30">
-        <v>78</v>
+      <c r="R8" s="39" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>3</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="31">
         <v>300</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="32">
         <v>135.5</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3466,7 +3472,7 @@
       <c r="C52" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="33" t="s">
         <v>1</v>
       </c>
       <c r="E52" s="15" t="s">
@@ -3513,7 +3519,7 @@
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B53" s="37"/>
+      <c r="B53" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
+++ b/backend/data/attachments/mobile/Liebherr_LTM1300.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\crane_lifting_capacity\data\mobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\crane_lifting_capacity\data\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3ECFFB-2127-4AF4-A3B0-1A84D1B3AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D6AEF4-A199-4598-880C-BE227A29FF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-6060" windowWidth="29040" windowHeight="15840" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
+    <workbookView xWindow="8565" yWindow="2070" windowWidth="28350" windowHeight="16470" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="23" r:id="rId1"/>
@@ -582,18 +582,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -603,9 +597,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,9 +606,6 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -633,9 +621,6 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -646,9 +631,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -705,9 +687,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1040,7 +1040,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="28" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="28">
         <v>14644.63</v>
       </c>
     </row>
@@ -1059,10 +1059,10 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="28" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="28">
         <v>1147.3800000000001</v>
       </c>
     </row>
@@ -1084,2442 +1084,2442 @@
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="29">
         <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="42"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="29"/>
-      <c r="C7" s="40" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="42"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="32">
         <v>14.7</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="32">
         <v>19.600000000000001</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="32">
         <v>24.4</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="32">
         <v>29.3</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="32">
         <v>34.200000000000003</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="32">
         <v>43.9</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="32">
         <v>48.7</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="32">
         <v>53.6</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="32">
         <v>58.5</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="32">
         <v>63.3</v>
       </c>
-      <c r="O8" s="38">
+      <c r="O8" s="32">
         <v>68.2</v>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="32">
         <v>73.099999999999994</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="32">
         <v>77.2</v>
       </c>
-      <c r="R8" s="39" t="s">
+      <c r="R8" s="33" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="B9" s="37">
         <v>3</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>300</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="26">
         <v>135.5</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4" t="s">
+      <c r="E9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="5">
+      <c r="B10" s="38">
         <v>3.5</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>183</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="13">
         <v>135.5</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>135.5</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8" t="s">
+      <c r="F10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
+      <c r="B11" s="39">
         <v>4</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <v>173.5</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="14">
         <v>135.5</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="8">
         <v>135.5</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <v>135.5</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="12" t="s">
+      <c r="G11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="5">
+      <c r="B12" s="38">
         <v>4.5</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>160.4</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="13">
         <v>135.5</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>135.5</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>135.5</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>112.6</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="8" t="s">
+      <c r="H12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
+      <c r="B13" s="39">
         <v>5</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="7">
         <v>147.80000000000001</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="14">
         <v>135.5</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <v>135</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>129.6</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="8">
         <v>112.2</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="8">
         <v>89.9</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="12" t="s">
+      <c r="I13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="5">
+      <c r="B14" s="38">
         <v>6</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>132.1</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="13">
         <v>126</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>124</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>117.3</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>110.1</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>89.1</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>72.3</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="8" t="s">
+      <c r="J14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9">
+      <c r="B15" s="39">
         <v>7</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="7">
         <v>119.6</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="14">
         <v>112.6</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <v>113.3</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="8">
         <v>106.9</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="8">
         <v>101.7</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="8">
         <v>87.7</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="8">
         <v>71.599999999999994</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="8">
         <v>59</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="12" t="s">
+      <c r="K15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="5">
+      <c r="B16" s="38">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>105.9</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="13">
         <v>100.3</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>101.2</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>98.6</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>93.2</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>86.3</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>70.900000000000006</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>58.6</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="5">
         <v>46.3</v>
       </c>
-      <c r="L16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R16" s="8" t="s">
+      <c r="L16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="9">
+      <c r="B17" s="39">
         <v>9</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="7">
         <v>93.6</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="14">
         <v>90.1</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="8">
         <v>91</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <v>90.8</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="8">
         <v>86.3</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="8">
         <v>83.2</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="8">
         <v>70.099999999999994</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="8">
         <v>58.1</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="8">
         <v>46.1</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="8">
         <v>37.200000000000003</v>
       </c>
-      <c r="M17" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O17" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P17" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17" s="12" t="s">
+      <c r="M17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="5">
+      <c r="B18" s="38">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="4">
         <v>83.6</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="13">
         <v>81.5</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>82.4</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <v>82.7</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <v>80.400000000000006</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <v>77.900000000000006</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <v>69.2</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="5">
         <v>57.7</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="5">
         <v>45.8</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="5">
         <v>37.1</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R18" s="8" t="s">
+      <c r="M18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="9">
+      <c r="B19" s="39">
         <v>11</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="7">
         <v>75.400000000000006</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="14">
         <v>74</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>74.8</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>75.2</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="8">
         <v>74.8</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="8">
         <v>72.900000000000006</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="8">
         <v>68.2</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="8">
         <v>57.2</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="8">
         <v>45.6</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="8">
         <v>37</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="8">
         <v>29.9</v>
       </c>
-      <c r="N19" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R19" s="12" t="s">
+      <c r="N19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="5">
+      <c r="B20" s="38">
         <v>12</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="4">
         <v>63.7</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="13">
         <v>63.7</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>68.3</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <v>68.599999999999994</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="5">
         <v>68.400000000000006</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="5">
         <v>68.400000000000006</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="5">
         <v>65.2</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="5">
         <v>56.4</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="5">
         <v>44.5</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="5">
         <v>36.6</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="5">
         <v>29.7</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="5">
         <v>24.5</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R20" s="8" t="s">
+      <c r="O20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="9">
+      <c r="B21" s="39">
         <v>13</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11">
+      <c r="C21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8">
         <v>62.4</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="8">
         <v>62.7</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="8">
         <v>62.6</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="8">
         <v>63.4</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="8">
         <v>61.4</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="8">
         <v>55.5</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="8">
         <v>43.1</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="8">
         <v>36.200000000000003</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="8">
         <v>29.5</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="8">
         <v>24.3</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="8">
         <v>19.8</v>
       </c>
-      <c r="P21" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R21" s="12" t="s">
+      <c r="P21" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="5">
+      <c r="B22" s="38">
         <v>14</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7">
+      <c r="C22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
         <v>57.9</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="5">
         <v>57.6</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="5">
         <v>58.7</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="5">
         <v>58.3</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="5">
         <v>57.5</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="5">
         <v>54.4</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="5">
         <v>41.4</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L22" s="5">
         <v>35.4</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="5">
         <v>29.2</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="5">
         <v>24.2</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O22" s="5">
         <v>19.8</v>
       </c>
-      <c r="P22" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R22" s="8" t="s">
+      <c r="P22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="9">
+      <c r="B23" s="39">
         <v>16</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11">
+      <c r="C23" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8">
         <v>49.7</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <v>50.4</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="8">
         <v>50.4</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="8">
         <v>49.9</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="8">
         <v>49.3</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="8">
         <v>49.7</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="8">
         <v>38</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="8">
         <v>33.299999999999997</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="8">
         <v>28.3</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="8">
         <v>23.8</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="8">
         <v>19.5</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="8">
         <v>16.5</v>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="8">
         <v>13.7</v>
       </c>
-      <c r="R23" s="12">
+      <c r="R23" s="9">
         <v>13.3</v>
       </c>
     </row>
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="5">
+      <c r="B24" s="38">
         <v>18</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="C24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5">
         <v>43.8</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="5">
         <v>43.9</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="5">
         <v>43.4</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="5">
         <v>44.4</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="5">
         <v>43.7</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="5">
         <v>35</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="5">
         <v>30.8</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="5">
         <v>26.7</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="5">
         <v>23</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="5">
         <v>18.899999999999999</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="5">
         <v>16.100000000000001</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="5">
         <v>13.6</v>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="6">
         <v>13.3</v>
       </c>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="9">
+      <c r="B25" s="39">
         <v>20</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="C25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8">
         <v>38.4</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="8">
         <v>38.4</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="8">
         <v>37.9</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="8">
         <v>39</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="8">
         <v>38.299999999999997</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="8">
         <v>32.200000000000003</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="8">
         <v>28.6</v>
       </c>
-      <c r="M25" s="11">
+      <c r="M25" s="8">
         <v>25</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="8">
         <v>21.9</v>
       </c>
-      <c r="O25" s="11">
+      <c r="O25" s="8">
         <v>18.3</v>
       </c>
-      <c r="P25" s="11">
+      <c r="P25" s="8">
         <v>15.6</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="8">
         <v>13.3</v>
       </c>
-      <c r="R25" s="12">
+      <c r="R25" s="9">
         <v>13.1</v>
       </c>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="5">
+      <c r="B26" s="38">
         <v>22</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="C26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5">
         <v>27.2</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="5">
         <v>33.9</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="5">
         <v>34.700000000000003</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="5">
         <v>34.5</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="5">
         <v>33.799999999999997</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="5">
         <v>29.7</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="5">
         <v>26.4</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="5">
         <v>23.4</v>
       </c>
-      <c r="N26" s="7">
+      <c r="N26" s="5">
         <v>20.7</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="5">
         <v>17.5</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="5">
         <v>15.1</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="Q26" s="5">
         <v>12.9</v>
       </c>
-      <c r="R26" s="8">
+      <c r="R26" s="6">
         <v>12.8</v>
       </c>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="9">
+      <c r="B27" s="39">
         <v>24</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="11">
+      <c r="C27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="8">
         <v>30.3</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="8">
         <v>31.2</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="8">
         <v>30.7</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="8">
         <v>30.1</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="8">
         <v>27.4</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="8">
         <v>24.5</v>
       </c>
-      <c r="M27" s="11">
+      <c r="M27" s="8">
         <v>21.9</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="8">
         <v>19.5</v>
       </c>
-      <c r="O27" s="11">
+      <c r="O27" s="8">
         <v>16.7</v>
       </c>
-      <c r="P27" s="11">
+      <c r="P27" s="8">
         <v>14.5</v>
       </c>
-      <c r="Q27" s="11">
+      <c r="Q27" s="8">
         <v>12.4</v>
       </c>
-      <c r="R27" s="12">
+      <c r="R27" s="9">
         <v>12.3</v>
       </c>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="5">
+      <c r="B28" s="38">
         <v>26</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="C28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
         <v>27.1</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="5">
         <v>28.1</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="5">
         <v>27.6</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="5">
         <v>26.9</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="5">
         <v>25.4</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="5">
         <v>22.7</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="5">
         <v>20.399999999999999</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="5">
         <v>18.399999999999999</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="5">
         <v>16</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="5">
         <v>13.8</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="5">
         <v>11.9</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="6">
         <v>11.8</v>
       </c>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="19">
+      <c r="B29" s="40">
         <v>28</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="21">
+      <c r="C29" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="16">
         <v>25.4</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="16">
         <v>24.9</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="16">
         <v>24.2</v>
       </c>
-      <c r="K29" s="21">
+      <c r="K29" s="16">
         <v>23.3</v>
       </c>
-      <c r="L29" s="21">
+      <c r="L29" s="16">
         <v>21.1</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M29" s="16">
         <v>19.100000000000001</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N29" s="16">
         <v>17.2</v>
       </c>
-      <c r="O29" s="21">
+      <c r="O29" s="16">
         <v>15.2</v>
       </c>
-      <c r="P29" s="21">
+      <c r="P29" s="16">
         <v>13.2</v>
       </c>
-      <c r="Q29" s="21">
+      <c r="Q29" s="16">
         <v>11.4</v>
       </c>
-      <c r="R29" s="22">
+      <c r="R29" s="17">
         <v>11.3</v>
       </c>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="24">
+      <c r="B30" s="41">
         <v>30</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="26">
+      <c r="C30" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20">
         <v>23.2</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="20">
         <v>22.6</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="20">
         <v>21.9</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="20">
         <v>21.2</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="20">
         <v>19.600000000000001</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="20">
         <v>17.8</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="20">
         <v>16.2</v>
       </c>
-      <c r="O30" s="26">
+      <c r="O30" s="20">
         <v>14.5</v>
       </c>
-      <c r="P30" s="26">
+      <c r="P30" s="20">
         <v>12.7</v>
       </c>
-      <c r="Q30" s="26">
+      <c r="Q30" s="20">
         <v>10.9</v>
       </c>
-      <c r="R30" s="28">
+      <c r="R30" s="22">
         <v>10.8</v>
       </c>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="9">
+      <c r="B31" s="39">
         <v>32</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="11">
+      <c r="C31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="8">
         <v>11.7</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="8">
         <v>20.6</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="8">
         <v>19.899999999999999</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="8">
         <v>19.7</v>
       </c>
-      <c r="L31" s="11">
+      <c r="L31" s="8">
         <v>18.2</v>
       </c>
-      <c r="M31" s="11">
+      <c r="M31" s="8">
         <v>16.7</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31" s="8">
         <v>15.2</v>
       </c>
-      <c r="O31" s="11">
+      <c r="O31" s="8">
         <v>13.8</v>
       </c>
-      <c r="P31" s="11">
+      <c r="P31" s="8">
         <v>12.1</v>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="8">
         <v>10.4</v>
       </c>
-      <c r="R31" s="12">
+      <c r="R31" s="9">
         <v>10.4</v>
       </c>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="5">
+      <c r="B32" s="38">
         <v>34</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="7">
+      <c r="C32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5">
         <v>18.899999999999999</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="5">
         <v>18.100000000000001</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="5">
         <v>18.8</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="5">
         <v>17</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="5">
         <v>15.6</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="5">
         <v>14.3</v>
       </c>
-      <c r="O32" s="7">
+      <c r="O32" s="5">
         <v>13.1</v>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="5">
         <v>11.6</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="Q32" s="5">
         <v>10</v>
       </c>
-      <c r="R32" s="8">
+      <c r="R32" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="9">
+      <c r="B33" s="39">
         <v>36</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="11">
+      <c r="C33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8">
         <v>15.7</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="8">
         <v>16.899999999999999</v>
       </c>
-      <c r="K33" s="11">
+      <c r="K33" s="8">
         <v>17.3</v>
       </c>
-      <c r="L33" s="11">
+      <c r="L33" s="8">
         <v>15.6</v>
       </c>
-      <c r="M33" s="11">
+      <c r="M33" s="8">
         <v>14.6</v>
       </c>
-      <c r="N33" s="11">
+      <c r="N33" s="8">
         <v>13.5</v>
       </c>
-      <c r="O33" s="11">
+      <c r="O33" s="8">
         <v>12.5</v>
       </c>
-      <c r="P33" s="11">
+      <c r="P33" s="8">
         <v>11.1</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="8">
         <v>9.6</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="9">
         <v>9.5</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="5">
+      <c r="B34" s="38">
         <v>38</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7">
+      <c r="C34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5">
         <v>16.3</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="5">
         <v>15.9</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="5">
         <v>14.6</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="5">
         <v>13.7</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="5">
         <v>12.7</v>
       </c>
-      <c r="O34" s="7">
+      <c r="O34" s="5">
         <v>11.8</v>
       </c>
-      <c r="P34" s="7">
+      <c r="P34" s="5">
         <v>10.6</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="Q34" s="5">
         <v>9.1999999999999993</v>
       </c>
-      <c r="R34" s="8">
+      <c r="R34" s="6">
         <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="9">
+      <c r="B35" s="39">
         <v>40</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="11">
+      <c r="C35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8">
         <v>14.8</v>
       </c>
-      <c r="K35" s="11">
+      <c r="K35" s="8">
         <v>14.6</v>
       </c>
-      <c r="L35" s="11">
+      <c r="L35" s="8">
         <v>13.7</v>
       </c>
-      <c r="M35" s="11">
+      <c r="M35" s="8">
         <v>12.8</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="8">
         <v>11.9</v>
       </c>
-      <c r="O35" s="11">
+      <c r="O35" s="8">
         <v>11.2</v>
       </c>
-      <c r="P35" s="11">
+      <c r="P35" s="8">
         <v>10.199999999999999</v>
       </c>
-      <c r="Q35" s="11">
+      <c r="Q35" s="8">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R35" s="12">
+      <c r="R35" s="9">
         <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="5">
+      <c r="B36" s="38">
         <v>42</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K36" s="7">
+      <c r="C36" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5">
         <v>13.5</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="5">
         <v>12.5</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="5">
         <v>11.9</v>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="5">
         <v>11.2</v>
       </c>
-      <c r="O36" s="7">
+      <c r="O36" s="5">
         <v>10.6</v>
       </c>
-      <c r="P36" s="7">
+      <c r="P36" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="Q36" s="7">
+      <c r="Q36" s="5">
         <v>8.5</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="6">
         <v>8.4</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="9">
+      <c r="B37" s="39">
         <v>44</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K37" s="11">
+      <c r="C37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K37" s="8">
         <v>12.4</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="8">
         <v>11.8</v>
       </c>
-      <c r="M37" s="11">
+      <c r="M37" s="8">
         <v>11.1</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="8">
         <v>10.5</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="8">
         <v>10</v>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="8">
         <v>9.4</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="8">
         <v>8.1</v>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="9">
         <v>8.1</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="5">
+      <c r="B38" s="38">
         <v>46</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K38" s="7">
+      <c r="C38" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K38" s="5">
         <v>8.8000000000000007</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="5">
         <v>11.4</v>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="5">
         <v>10.5</v>
       </c>
-      <c r="N38" s="7">
+      <c r="N38" s="5">
         <v>9.9</v>
       </c>
-      <c r="O38" s="7">
+      <c r="O38" s="5">
         <v>9.5</v>
       </c>
-      <c r="P38" s="7">
+      <c r="P38" s="5">
         <v>9</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="Q38" s="5">
         <v>7.8</v>
       </c>
-      <c r="R38" s="8">
+      <c r="R38" s="6">
         <v>7.7</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="9">
+      <c r="B39" s="39">
         <v>48</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L39" s="11">
+      <c r="C39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" s="8">
         <v>11</v>
       </c>
-      <c r="M39" s="11">
+      <c r="M39" s="8">
         <v>9.9</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39" s="8">
         <v>9.1999999999999993</v>
       </c>
-      <c r="O39" s="11">
+      <c r="O39" s="8">
         <v>9</v>
       </c>
-      <c r="P39" s="11">
+      <c r="P39" s="8">
         <v>8.6</v>
       </c>
-      <c r="Q39" s="11">
+      <c r="Q39" s="8">
         <v>7.5</v>
       </c>
-      <c r="R39" s="12">
+      <c r="R39" s="9">
         <v>7.3</v>
       </c>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="5">
+      <c r="B40" s="38">
         <v>50</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L40" s="7">
+      <c r="C40" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L40" s="5">
         <v>8.6</v>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="5">
         <v>9.1</v>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="5">
         <v>8.6999999999999993</v>
       </c>
-      <c r="O40" s="7">
+      <c r="O40" s="5">
         <v>8.5</v>
       </c>
-      <c r="P40" s="7">
+      <c r="P40" s="5">
         <v>8.1999999999999993</v>
       </c>
-      <c r="Q40" s="7">
+      <c r="Q40" s="5">
         <v>7.1</v>
       </c>
-      <c r="R40" s="8">
+      <c r="R40" s="6">
         <v>6.9</v>
       </c>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="9">
+      <c r="B41" s="39">
         <v>52</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M41" s="11">
+      <c r="C41" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41" s="8">
         <v>8.6</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41" s="8">
         <v>8.3000000000000007</v>
       </c>
-      <c r="O41" s="11">
+      <c r="O41" s="8">
         <v>8</v>
       </c>
-      <c r="P41" s="11">
+      <c r="P41" s="8">
         <v>7.8</v>
       </c>
-      <c r="Q41" s="11">
+      <c r="Q41" s="8">
         <v>6.8</v>
       </c>
-      <c r="R41" s="12">
+      <c r="R41" s="9">
         <v>6.6</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="5">
+      <c r="B42" s="38">
         <v>54</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M42" s="7">
+      <c r="C42" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" s="5">
         <v>8.3000000000000007</v>
       </c>
-      <c r="N42" s="7">
+      <c r="N42" s="5">
         <v>7.9</v>
       </c>
-      <c r="O42" s="7">
+      <c r="O42" s="5">
         <v>7.5</v>
       </c>
-      <c r="P42" s="7">
+      <c r="P42" s="5">
         <v>7.4</v>
       </c>
-      <c r="Q42" s="7">
+      <c r="Q42" s="5">
         <v>6.5</v>
       </c>
-      <c r="R42" s="8">
+      <c r="R42" s="6">
         <v>6.2</v>
       </c>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="9">
+      <c r="B43" s="39">
         <v>56</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M43" s="11">
+      <c r="C43" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43" s="8">
         <v>7.5</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O43" s="8">
         <v>7.1</v>
       </c>
-      <c r="P43" s="11">
+      <c r="P43" s="8">
         <v>7</v>
       </c>
-      <c r="Q43" s="11">
+      <c r="Q43" s="8">
         <v>6.3</v>
       </c>
-      <c r="R43" s="12">
+      <c r="R43" s="9">
         <v>5.8</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="5">
+      <c r="B44" s="38">
         <v>58</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N44" s="7">
+      <c r="C44" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44" s="5">
         <v>6.9</v>
       </c>
-      <c r="O44" s="7">
+      <c r="O44" s="5">
         <v>6.8</v>
       </c>
-      <c r="P44" s="7">
+      <c r="P44" s="5">
         <v>6.6</v>
       </c>
-      <c r="Q44" s="7">
+      <c r="Q44" s="5">
         <v>6</v>
       </c>
-      <c r="R44" s="8">
+      <c r="R44" s="6">
         <v>5.5</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="9">
+      <c r="B45" s="39">
         <v>60</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N45" s="11">
+      <c r="C45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45" s="8">
         <v>5</v>
       </c>
-      <c r="O45" s="11">
+      <c r="O45" s="8">
         <v>6.5</v>
       </c>
-      <c r="P45" s="11">
+      <c r="P45" s="8">
         <v>6.2</v>
       </c>
-      <c r="Q45" s="11">
+      <c r="Q45" s="8">
         <v>5.7</v>
       </c>
-      <c r="R45" s="12">
+      <c r="R45" s="9">
         <v>5.2</v>
       </c>
     </row>
     <row r="46" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="5">
+      <c r="B46" s="38">
         <v>62</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O46" s="7">
+      <c r="C46" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5">
         <v>6.3</v>
       </c>
-      <c r="P46" s="7">
+      <c r="P46" s="5">
         <v>5.7</v>
       </c>
-      <c r="Q46" s="7">
+      <c r="Q46" s="5">
         <v>5.4</v>
       </c>
-      <c r="R46" s="8">
+      <c r="R46" s="6">
         <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="9">
+      <c r="B47" s="39">
         <v>64</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O47" s="11">
+      <c r="C47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8">
         <v>4.7</v>
       </c>
-      <c r="P47" s="11">
+      <c r="P47" s="8">
         <v>5.2</v>
       </c>
-      <c r="Q47" s="11">
+      <c r="Q47" s="8">
         <v>5.2</v>
       </c>
-      <c r="R47" s="12">
+      <c r="R47" s="9">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="5">
+      <c r="B48" s="38">
         <v>66</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P48" s="7">
+      <c r="C48" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P48" s="5">
         <v>4.7</v>
       </c>
-      <c r="Q48" s="7">
+      <c r="Q48" s="5">
         <v>4.8</v>
       </c>
-      <c r="R48" s="8">
+      <c r="R48" s="6">
         <v>4.3</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="19">
+      <c r="B49" s="40">
         <v>68</v>
       </c>
-      <c r="C49" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="K49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="L49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="M49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="O49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="P49" s="21">
+      <c r="C49" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="P49" s="16">
         <v>3.8</v>
       </c>
-      <c r="Q49" s="21">
+      <c r="Q49" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="R49" s="22">
+      <c r="R49" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="24">
+      <c r="B50" s="41">
         <v>70</v>
       </c>
-      <c r="C50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="K50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="P50" s="26">
+      <c r="C50" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" s="20">
         <v>1.5</v>
       </c>
-      <c r="Q50" s="26">
+      <c r="Q50" s="20">
         <v>4</v>
       </c>
-      <c r="R50" s="28">
+      <c r="R50" s="22">
         <v>3.8</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="9">
+      <c r="B51" s="39">
         <v>72</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="P51" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="11">
+      <c r="C51" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="8">
         <v>3.2</v>
       </c>
-      <c r="R51" s="12">
+      <c r="R51" s="9">
         <v>3.4</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="13">
+      <c r="B52" s="42">
         <v>74</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="L52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="N52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="O52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="P52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="R52" s="16">
+      <c r="C52" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="P52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="R52" s="12">
         <v>1.9</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B53" s="34"/>
+      <c r="B53" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
